--- a/forms/trg/Formulir_TRG_criminological.xlsx
+++ b/forms/trg/Formulir_TRG_criminological.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B20)</f>
+        <f>COUNTA(Anggota!B5:B21)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F20)</f>
+        <f>COUNTA(Anggota!F5:F21)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,10 +937,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muh. Djaelani Prasetya, S.H., M.H.</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n"/>
+          <t>Ahsan Yunus, S.H., M.H.</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
@@ -962,7 +966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>M. Aris Munandar, S.H., M.H.</t>
+          <t>Muh. Djaelani Prasetya, S.H., M.H.</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
@@ -987,7 +991,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dede Arwinsyah, S.H., M.H.</t>
+          <t>M. Aris Munandar, S.H., M.H.</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
@@ -1012,15 +1016,11 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Bayu Arjunah, S.H., M.H.</t>
+          <t>Dede Arwinsyah, S.H., M.H.</t>
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>The Criminological Justice Research Group (CJRG), based in the Criminal Law Department of Hasanuddin University's Faculty of Law, is a research collective dedicated to bridging academic research and practical applications in criminology and criminal justice by exploring innovative methodologies, fostering multidisciplinary collaboration, and enhancing crime prevention, legal reform, and justice delivery for safer communities and equitable legal processes.</t>
-        </is>
-      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
@@ -1039,9 +1039,17 @@
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="n"/>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Bayu Arjunah, S.H., M.H.</t>
+        </is>
+      </c>
       <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>The Criminological Justice Research Group (CJRG), based in the Criminal Law Department of Hasanuddin University's Faculty of Law, is a research collective dedicated to bridging academic research and practical applications in criminology and criminal justice by exploring innovative methodologies, fostering multidisciplinary collaboration, and enhancing crime prevention, legal reform, and justice delivery for safer communities and equitable legal processes.</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1050,7 +1058,11 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1239,15 +1251,32 @@
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="12" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
